--- a/nr-update-cycle/ig/ValueSet-fr-core-vs-organization-etablissement-type.xlsx
+++ b/nr-update-cycle/ig/ValueSet-fr-core-vs-organization-etablissement-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:47:13+00:00</t>
+    <t>2026-06-12T13:49:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-cycle/ig/ValueSet-fr-core-vs-organization-etablissement-type.xlsx
+++ b/nr-update-cycle/ig/ValueSet-fr-core-vs-organization-etablissement-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:49:15+00:00</t>
+    <t>2026-06-12T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
